--- a/results/Int Task Remove ACC -0.3/Rando_5_permute.xlsx
+++ b/results/Int Task Remove ACC -0.3/Rando_5_permute.xlsx
@@ -440,863 +440,863 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7867902606382331</v>
+        <v>0.7710765368815063</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7877505707924587</v>
+        <v>0.7749475844225364</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7861831726733364</v>
+        <v>0.7696383021002728</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7861831726733364</v>
+        <v>0.7724794899974452</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7953083495885833</v>
+        <v>0.7708624136714426</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7965821393666332</v>
+        <v>0.7778583218093411</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7937608227522133</v>
+        <v>0.775176104174186</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7925069042569155</v>
+        <v>0.7767733092174365</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7896955232838714</v>
+        <v>0.7725788464112058</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.785052942774761</v>
+        <v>0.7754001630256259</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7864161533251955</v>
+        <v>0.7754001630256259</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7864161533251955</v>
+        <v>0.7431614399785877</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7892374699396156</v>
+        <v>0.7469530023886093</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7992986248261262</v>
+        <v>0.7537899402644908</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7985072205752939</v>
+        <v>0.7338872284426998</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7996364366329125</v>
+        <v>0.7137803290522209</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8162399072132757</v>
+        <v>0.7510535835222457</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8053277342276762</v>
+        <v>0.7529443969065686</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7926052468297193</v>
+        <v>0.7529443969065686</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7903458008735254</v>
+        <v>0.6888187536244814</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.790042256891077</v>
+        <v>0.6933465673372887</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7928933804296252</v>
+        <v>0.6908685372708212</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8082086646903527</v>
+        <v>0.6802708577500031</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8082086646903527</v>
+        <v>0.6634234570354479</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8138016197123125</v>
+        <v>0.6826440566615434</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7843817800613981</v>
+        <v>0.6688266210303058</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7789234631184937</v>
+        <v>0.7406193351636542</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.782665347321635</v>
+        <v>0.728304209062116</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7844115869855264</v>
+        <v>0.7312402924728392</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7840981073617019</v>
+        <v>0.7448391439938034</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7871722759107334</v>
+        <v>0.7465257698094385</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7884957438956637</v>
+        <v>0.7127713545320719</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.778922449277537</v>
+        <v>0.7231802568667448</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7895256035395215</v>
+        <v>0.7365053713293888</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7723592484599756</v>
+        <v>0.7034221187653851</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7886382899341815</v>
+        <v>0.7415080681463337</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8030628135303159</v>
+        <v>0.7415080681463337</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8156074732244603</v>
+        <v>0.7395775121965067</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8077009331392166</v>
+        <v>0.7348708569389303</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.8143932972946668</v>
+        <v>0.7348708569389303</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.8203836779716692</v>
+        <v>0.7348708569389303</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.8232591336931793</v>
+        <v>0.7415080681463337</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8233187475414356</v>
+        <v>0.7416824487908933</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8233187475414356</v>
+        <v>0.7258515250195672</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8236873801133069</v>
+        <v>0.7887033785236042</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8118655890213191</v>
+        <v>0.7957931683340971</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8117761682489344</v>
+        <v>0.7891360858439415</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8002921889637329</v>
+        <v>0.7881723286304632</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8015659787417828</v>
+        <v>0.7599964718334706</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7849515586790869</v>
+        <v>0.7401876416842736</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.7907089587042302</v>
+        <v>0.6654643188813685</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.7939232400734832</v>
+        <v>0.6683596458856307</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.7936196960910349</v>
+        <v>0.6655880074780909</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.7774544075721753</v>
+        <v>0.6751513664548414</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7558606090345394</v>
+        <v>0.6751513664548414</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7076871449022049</v>
+        <v>0.7078803829885598</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.7184249372432447</v>
+        <v>0.6226786083613491</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.7197484052281751</v>
+        <v>0.6319980372039078</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7052642677837841</v>
+        <v>0.6289228548139196</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7052642677837841</v>
+        <v>0.6250319359901373</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7121752160495078</v>
+        <v>0.6250319359901373</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.7082147477360932</v>
+        <v>0.6250319359901373</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.7334510740631095</v>
+        <v>0.6358194065380576</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7334510740631095</v>
+        <v>0.5906679995295778</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7111597529472357</v>
+        <v>0.5540878067375814</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7055822083078184</v>
+        <v>0.5528140169595315</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7088262966011996</v>
+        <v>0.5569190589933776</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7107469169096505</v>
+        <v>0.5704627575662951</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7129357995352553</v>
+        <v>0.5585063283952519</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.6776790747281892</v>
+        <v>0.5650894004955654</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.6867093561298852</v>
+        <v>0.5689097559887586</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.6760688925206926</v>
+        <v>0.6059425273838442</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5681540389396035</v>
+        <v>0.6274458913081387</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5421372578440875</v>
+        <v>0.6198737159704283</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5419430059167758</v>
+        <v>0.6356659110172069</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5146112731003663</v>
+        <v>0.6407213275639024</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5137160515355635</v>
+        <v>0.5714672711862344</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5372061381986885</v>
+        <v>0.5217979861063236</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5052342580914647</v>
+        <v>0.5192106639847194</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5003333509065766</v>
+        <v>0.5149764586129845</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4996964560175516</v>
+        <v>0.5178573890756609</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5003333509065766</v>
+        <v>0.5126628735497005</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4990694967699027</v>
+        <v>0.5058612173391136</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5000496782068803</v>
+        <v>0.5078017089303166</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4997163273003037</v>
+        <v>0.4997063916589277</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4997163273003037</v>
+        <v>0.4990794324112788</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -1306,21 +1306,21 @@
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5003234152652005</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5003234152652005</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
